--- a/santi/成就表.xlsx
+++ b/santi/成就表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ROG\Desktop\三体\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E557C8B-A684-4A0F-9AD8-0028E960C34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED344D01-D99B-4D5C-8305-EF203B34FEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="394">
   <si>
     <t>名称</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1486,55 +1486,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>新号别搞</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>文明在第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>次观星时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>毁灭</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>return ctx.event === 'death' &amp;&amp; ctx.civilizationYears === 0;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>这期拉了</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1715,26 +1666,6 @@
   </si>
   <si>
     <t>发现金鱼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>降临</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>科学边界</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理学不存在了</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷德王</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>永恒的终结</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2154,7 +2085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr defaultColWidth="15.33203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="16384" width="15.33203125" style="2"/>
@@ -3889,7 +3820,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="55" customHeight="1" thickBot="1">
+    <row r="115" spans="1:5" ht="55" customHeight="1">
       <c r="A115" s="2" t="s">
         <v>344</v>
       </c>
@@ -3906,27 +3837,29 @@
         <v>346</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="55" customHeight="1" thickBot="1">
-      <c r="A116" s="4" t="s">
+    <row r="116" spans="1:5" ht="65" customHeight="1">
+      <c r="A116" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B116" s="4">
-        <v>1</v>
-      </c>
-      <c r="C116" s="5" t="s">
+      <c r="B116" s="2">
+        <v>3</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="D116" s="4"/>
-      <c r="E116" s="6" t="s">
+      <c r="D116" s="2">
+        <v>1</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="65" customHeight="1">
+    <row r="117" spans="1:5" ht="55" customHeight="1">
       <c r="A117" s="2" t="s">
         <v>350</v>
       </c>
       <c r="B117" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>351</v>
@@ -3943,7 +3876,7 @@
         <v>353</v>
       </c>
       <c r="B118" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>354</v>
@@ -3960,13 +3893,10 @@
         <v>356</v>
       </c>
       <c r="B119" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="D119" s="2">
-        <v>1</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>358</v>
@@ -3982,6 +3912,9 @@
       <c r="C120" s="2" t="s">
         <v>360</v>
       </c>
+      <c r="D120" s="2">
+        <v>1</v>
+      </c>
       <c r="E120" s="2" t="s">
         <v>361</v>
       </c>
@@ -3991,7 +3924,7 @@
         <v>362</v>
       </c>
       <c r="B121" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>363</v>
@@ -4008,13 +3941,10 @@
         <v>365</v>
       </c>
       <c r="B122" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="D122" s="2">
-        <v>1</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>367</v>
@@ -4030,6 +3960,9 @@
       <c r="C123" s="2" t="s">
         <v>369</v>
       </c>
+      <c r="D123" s="2">
+        <v>1</v>
+      </c>
       <c r="E123" s="2" t="s">
         <v>370</v>
       </c>
@@ -4056,7 +3989,7 @@
         <v>374</v>
       </c>
       <c r="B125" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>375</v>
@@ -4073,7 +4006,7 @@
         <v>377</v>
       </c>
       <c r="B126" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>378</v>
@@ -4090,7 +4023,7 @@
         <v>380</v>
       </c>
       <c r="B127" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>381</v>
@@ -4107,7 +4040,7 @@
         <v>383</v>
       </c>
       <c r="B128" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>384</v>
@@ -4124,7 +4057,7 @@
         <v>386</v>
       </c>
       <c r="B129" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>387</v>
@@ -4141,13 +4074,10 @@
         <v>389</v>
       </c>
       <c r="B130" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="D130" s="2">
-        <v>1</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>391</v>
@@ -4158,52 +4088,13 @@
         <v>392</v>
       </c>
       <c r="B131" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="E131" s="2" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" ht="55" customHeight="1">
-      <c r="A132" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B132" s="2">
-        <v>3</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="D132" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" ht="55" customHeight="1">
-      <c r="A134" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" ht="55" customHeight="1">
-      <c r="A135" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" ht="55" customHeight="1">
-      <c r="A136" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" ht="55" customHeight="1">
-      <c r="A137" s="2" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" ht="55" customHeight="1">
-      <c r="A138" s="2" t="s">
-        <v>401</v>
+      <c r="D131" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
